--- a/activity/M03A04/M03A04_Modelacion1D.xlsx
+++ b/activity/M03A04/M03A04_Modelacion1D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1B28E74-5731-490D-8930-0E661BD0F32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4293A2D8-8F51-47FA-BCD3-B077C1961144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Detalle" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Detalle!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="31">
   <si>
     <t>Observaciones</t>
   </si>
@@ -54,18 +54,6 @@
   </si>
   <si>
     <t>Valor</t>
-  </si>
-  <si>
-    <t>Luego de modificación del modelo y la ejecución completa en condiciones de flujo permanente y no permanente, comprimir como HECRAS_v1.zip</t>
-  </si>
-  <si>
-    <t>Crear un único reporte en Adobe Acrobat que muestre capturas de pantalla detalladas del proceso de modelación con perfiles de cada río, secciones de inicio y entrega del cauce sinuoso diseñado, la planta original del modelo y la planta con las modificaciones realizadas para modelar establemente a flujo no permanente, nombrar como HCMC0024_HECRAS.pdf. Incluir portada, tabla de contenido, numeración de páginas y observaciones detalladas.</t>
-  </si>
-  <si>
-    <t>Flujo no permanente: para el modelo como HECRAS_v1, ejecutar la modelación en condiciones de flujo permanente para 2.33, 25, 100 años de periodo de retorno y los periodos de retorno considerados en la entrega anterior del proyecto final, presentar el perfil de flujo de la envolvente de máximos del cauce principal, los cauces laterales y las secciones naturales y de diseño de inicio y entrega con todas las profundidades de lámina de agua máximos para todos los periodos de retorno evaluados. En caso de que no pueda ser ejecutado en flujo no permanente, crear una copia de la geometría, depurar o eliminar secciones naturales donde se presentan controles de flujo hasta obtener un modelo estable en esta condición. En el reporte integrado indicar las consideraciones generales para la modificación de la geometría del modelo hidráulico.</t>
-  </si>
-  <si>
-    <t>Flujo permanente: para el modelo HECRAS_v1, ejecutar la modelación en condiciones de flujo permanente para los periodos de retorno considerados en la entrega anterior del proyecto final, presentar el perfil de flujo del cauce principal, los cauces laterales, localización de profundidades críticas y para las secciones naturales y de diseño de inicio y entrega mostrar las profundidades de lámina de agua para todos los periodos de retorno evaluados, caudal medio y caudal ecológico.</t>
   </si>
   <si>
     <t>Calificar sobre</t>
@@ -93,9 +81,6 @@
   </si>
   <si>
     <t>Grupo 5</t>
-  </si>
-  <si>
-    <t>Considere, analice y explique el tipo o los tipos de regímenes de flujo a aplicar a partir de los posible controles hidráulicos que existen en el canal. Indicar la abscisa de las secciones transversales donde se presentan los posibles controles. Analizar a partir de las profundidades críticas obtenidas en la modelación de flujo permanente. (opcional)</t>
   </si>
   <si>
     <t>Calificación: 3.4. Modelación unidimensional en condiciones de flujo permanente y no permanente</t>
@@ -129,6 +114,24 @@
   </si>
   <si>
     <t>Grupo 14</t>
+  </si>
+  <si>
+    <t>Luego de la modificación del modelo y la ejecución completa en condiciones de flujo permanente y no permanente, comprimir como HECRAS_v1_aaaammdd.zip.</t>
+  </si>
+  <si>
+    <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto.</t>
+  </si>
+  <si>
+    <t>En caso de haber realizado modificaciones a la geometría obtenida del modelo RAS-Mapper, deberán existir dos archivos de geometría, uno con la geometría original y otro con la geometría depurada.</t>
+  </si>
+  <si>
+    <t>Considere, analice y explique el tipo o los tipos de regímenes de flujo a aplicar a partir de los posible controles hidráulicos que existen en el canal. Indicar la abscisa de las secciones transversales donde se presentan los posibles controles. Analizar a partir de las profundidades críticas obtenidas en la modelación de flujo permanente.</t>
+  </si>
+  <si>
+    <t>Flujo permanente: en el modelo HECRAS_v1, ejecutar la modelación hidráulica en condiciones de flujo permanente para los periodos de retorno considerados en su diseño, presentar el perfil de flujo del cauce principal, los cauces laterales, localización de profundidades críticas y para las secciones naturales de inicio y entrega del realineamiento, mostrar las profundidades de lámina de agua para todos los periodos de retorno evaluados, caudal medio y caudal ecológico.</t>
+  </si>
+  <si>
+    <t>Flujo no permanente: en el modelo como HECRAS_v1, ejecutar la modelación hidráulica en condiciones de flujo no permanente para 2.33, 25, 100 años de periodo de retorno y los periodos de retorno considerados en su diseño, presentar el perfil de flujo de la envolvente de máximos del cauce principal, los cauces laterales y para las secciones naturales y de diseño de inicio y entrega, mostrar todas las profundidades de lámina de agua máximos para todos los periodos de retorno evaluados. En caso de que no pueda ser ejecutado en flujo no permanente, crear una copia de la geometría, depurar o eliminar secciones naturales donde se presentan controles de flujo, hasta obtener un modelo estable en esta condición. En el informe técnico indicar las consideraciones generales para la modificación de la geometría del modelo hidráulico.</t>
   </si>
 </sst>
 </file>
@@ -242,7 +245,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -412,6 +415,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -419,18 +446,46 @@
       <top style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -442,7 +497,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -484,9 +539,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -520,7 +572,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -530,15 +582,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -578,6 +621,30 @@
     </xf>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1996,304 +2063,304 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="39" t="s">
-        <v>20</v>
+      <c r="F1" s="35" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="B2" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>10</v>
+      <c r="C4" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="40">
+        <v>9</v>
+      </c>
+      <c r="C5" s="36">
         <v>5</v>
       </c>
-      <c r="D5" s="21">
-        <f>Detalle!C10*C5/5</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="22">
+      <c r="D5" s="20">
+        <f>Detalle!C11*C5/5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="36"/>
+      <c r="F5" s="21">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="40">
+        <v>10</v>
+      </c>
+      <c r="C6" s="36">
         <v>5</v>
       </c>
-      <c r="D6" s="21">
-        <f>Detalle!F10*C6/5</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="22">
+      <c r="D6" s="20">
+        <f>Detalle!F11*C6/5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="36"/>
+      <c r="F6" s="21">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="40">
+        <v>12</v>
+      </c>
+      <c r="C7" s="36">
         <v>5</v>
       </c>
-      <c r="D7" s="21">
-        <f>Detalle!I10*C7/5</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="22">
+      <c r="D7" s="20">
+        <f>Detalle!I11*C7/5</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="36"/>
+      <c r="F7" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="40">
+        <v>11</v>
+      </c>
+      <c r="C8" s="36">
         <v>5</v>
       </c>
-      <c r="D8" s="21">
-        <f>Detalle!L10*C8/5</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="22">
+      <c r="D8" s="20">
+        <f>Detalle!L11*C8/5</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="36"/>
+      <c r="F8" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="40">
+        <v>13</v>
+      </c>
+      <c r="C9" s="36">
         <v>5</v>
       </c>
-      <c r="D9" s="21">
-        <f>Detalle!O10*C9/5</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="22">
+      <c r="D9" s="20">
+        <f>Detalle!O11*C9/5</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="36"/>
+      <c r="F9" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="40">
+        <v>16</v>
+      </c>
+      <c r="C10" s="36">
         <v>5</v>
       </c>
-      <c r="D10" s="21">
-        <f>Detalle!R10*C10/5</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="22">
+      <c r="D10" s="20">
+        <f>Detalle!R11*C10/5</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="40">
+        <v>17</v>
+      </c>
+      <c r="C11" s="36">
         <v>5</v>
       </c>
-      <c r="D11" s="21">
-        <f>Detalle!U10*C11/5</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="22">
+      <c r="D11" s="20">
+        <f>Detalle!U11*C11/5</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="40">
+        <v>18</v>
+      </c>
+      <c r="C12" s="36">
         <v>5</v>
       </c>
-      <c r="D12" s="21">
-        <f>Detalle!X10*C12/5</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="22">
+      <c r="D12" s="20">
+        <f>Detalle!X11*C12/5</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="36"/>
+      <c r="F12" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="40">
+        <v>19</v>
+      </c>
+      <c r="C13" s="36">
         <v>5</v>
       </c>
-      <c r="D13" s="21">
-        <f>Detalle!AA10*C13/5</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="22">
+      <c r="D13" s="20">
+        <f>Detalle!AA11*C13/5</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="36"/>
+      <c r="F13" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="40">
+        <v>20</v>
+      </c>
+      <c r="C14" s="36">
         <v>5</v>
       </c>
-      <c r="D14" s="21">
-        <f>Detalle!AD10*C14/5</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="22">
+      <c r="D14" s="20">
+        <f>Detalle!AD11*C14/5</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="F14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="40">
+        <v>21</v>
+      </c>
+      <c r="C15" s="36">
         <v>5</v>
       </c>
-      <c r="D15" s="21">
-        <f>Detalle!AG10*C15/5</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="22">
+      <c r="D15" s="20">
+        <f>Detalle!AG11*C15/5</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="36"/>
+      <c r="F15" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="40">
+        <v>22</v>
+      </c>
+      <c r="C16" s="36">
         <v>5</v>
       </c>
-      <c r="D16" s="21">
-        <f>Detalle!AJ10*C16/5</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="40"/>
-      <c r="F16" s="22">
+      <c r="D16" s="20">
+        <f>Detalle!AJ11*C16/5</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="36"/>
+      <c r="F16" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="40">
+        <v>23</v>
+      </c>
+      <c r="C17" s="36">
         <v>5</v>
       </c>
-      <c r="D17" s="21">
-        <f>Detalle!AM10*C17/5</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="22">
+      <c r="D17" s="20">
+        <f>Detalle!AM11*C17/5</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="36"/>
+      <c r="F17" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="41">
+      <c r="B18" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="37">
         <v>5</v>
       </c>
-      <c r="D18" s="36">
-        <f>Detalle!AP10*C18/5</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="37">
+      <c r="D18" s="32">
+        <f>Detalle!AP11*C18/5</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="37"/>
+      <c r="F18" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="38" t="str">
+      <c r="B19" s="34" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M03A04 en GitHub.</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2311,7 +2378,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17987CE-896A-4E26-83D1-1610B3259376}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AR46"/>
+  <dimension ref="A1:AR47"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="10" customWidth="1"/>
@@ -2385,668 +2452,670 @@
     </row>
     <row r="2" spans="1:44" s="11" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10"/>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="27" t="str">
+      <c r="C2" s="26" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="27" t="str">
+      <c r="D2" s="27"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="26" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="27" t="str">
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="26" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="28"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="27" t="str">
+      <c r="J2" s="27"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="26" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="27" t="str">
+      <c r="M2" s="27"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="26" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="27" t="str">
+      <c r="P2" s="27"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="26" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="28"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="27" t="str">
+      <c r="S2" s="27"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="26" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="28"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="27" t="str">
+      <c r="V2" s="27"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="26" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="27" t="str">
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="26" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="27" t="str">
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="26" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="27" t="str">
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="26" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="27" t="str">
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="26" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="29"/>
-      <c r="AM2" s="27" t="str">
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="26" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="29"/>
-      <c r="AP2" s="27" t="str">
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="26" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="29"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="28"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="34"/>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15" t="s">
+      <c r="E3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="H3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="15" t="s">
+      <c r="K3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="M3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="O3" s="15" t="s">
+      <c r="N3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="O3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="P3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="15" t="s">
+      <c r="Q3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="15" t="s">
+      <c r="T3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="V3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="W3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="X3" s="15" t="s">
+      <c r="W3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="Y3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="15" t="s">
+      <c r="Z3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="AB3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AC3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="15" t="s">
+      <c r="AC3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="AE3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AF3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="15" t="s">
+      <c r="AF3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="AH3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AI3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="15" t="s">
+      <c r="AI3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="AK3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AL3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="15" t="s">
+      <c r="AL3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="AN3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AO3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="15" t="s">
+      <c r="AO3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="14" t="s">
         <v>1</v>
       </c>
       <c r="AQ3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AR3" s="16" t="s">
+      <c r="AR3" s="15" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="111.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="42">
-        <v>0</v>
-      </c>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="42">
-        <v>0</v>
-      </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="42">
-        <v>0</v>
-      </c>
-      <c r="J4" s="43"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="42">
-        <v>0</v>
-      </c>
-      <c r="M4" s="43"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="42">
-        <v>0</v>
-      </c>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="42">
-        <v>0</v>
-      </c>
-      <c r="S4" s="43"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="42">
-        <v>0</v>
-      </c>
-      <c r="V4" s="43"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="42">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="42">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="42">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="43"/>
-      <c r="AF4" s="44"/>
-      <c r="AG4" s="42">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="43"/>
-      <c r="AI4" s="44"/>
-      <c r="AJ4" s="42">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="43"/>
-      <c r="AL4" s="44"/>
-      <c r="AM4" s="42">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="43"/>
-      <c r="AO4" s="44"/>
-      <c r="AP4" s="42">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="43"/>
-      <c r="AR4" s="44"/>
+        <v>29</v>
+      </c>
+      <c r="C4" s="38">
+        <v>0</v>
+      </c>
+      <c r="D4" s="39"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="38">
+        <v>0</v>
+      </c>
+      <c r="G4" s="39"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="38">
+        <v>0</v>
+      </c>
+      <c r="J4" s="39"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="38">
+        <v>0</v>
+      </c>
+      <c r="M4" s="39"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="38">
+        <v>0</v>
+      </c>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="38">
+        <v>0</v>
+      </c>
+      <c r="S4" s="39"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="38">
+        <v>0</v>
+      </c>
+      <c r="V4" s="39"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="38">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="38">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="39"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="38">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="39"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="38">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="39"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="38">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="39"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="38">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="39"/>
+      <c r="AO4" s="40"/>
+      <c r="AP4" s="38">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="39"/>
+      <c r="AR4" s="40"/>
     </row>
     <row r="5" spans="1:44" ht="184.5" x14ac:dyDescent="0.45">
       <c r="B5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="43"/>
-      <c r="Z5" s="44"/>
-      <c r="AA5" s="42"/>
-      <c r="AB5" s="43"/>
-      <c r="AC5" s="44"/>
-      <c r="AD5" s="42"/>
-      <c r="AE5" s="43"/>
-      <c r="AF5" s="44"/>
-      <c r="AG5" s="42"/>
-      <c r="AH5" s="43"/>
-      <c r="AI5" s="44"/>
-      <c r="AJ5" s="42"/>
-      <c r="AK5" s="43"/>
-      <c r="AL5" s="44"/>
-      <c r="AM5" s="42"/>
-      <c r="AN5" s="43"/>
-      <c r="AO5" s="44"/>
-      <c r="AP5" s="42"/>
-      <c r="AQ5" s="43"/>
-      <c r="AR5" s="44"/>
+        <v>30</v>
+      </c>
+      <c r="C5" s="38"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="40"/>
+      <c r="X5" s="38"/>
+      <c r="Y5" s="39"/>
+      <c r="Z5" s="40"/>
+      <c r="AA5" s="38"/>
+      <c r="AB5" s="39"/>
+      <c r="AC5" s="40"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="39"/>
+      <c r="AF5" s="40"/>
+      <c r="AG5" s="38"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="40"/>
+      <c r="AJ5" s="38"/>
+      <c r="AK5" s="39"/>
+      <c r="AL5" s="40"/>
+      <c r="AM5" s="38"/>
+      <c r="AN5" s="39"/>
+      <c r="AO5" s="40"/>
+      <c r="AP5" s="38"/>
+      <c r="AQ5" s="39"/>
+      <c r="AR5" s="40"/>
     </row>
     <row r="6" spans="1:44" ht="80.650000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="44"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="43"/>
-      <c r="Z6" s="44"/>
-      <c r="AA6" s="42"/>
-      <c r="AB6" s="43"/>
-      <c r="AC6" s="44"/>
-      <c r="AD6" s="42"/>
-      <c r="AE6" s="43"/>
-      <c r="AF6" s="44"/>
-      <c r="AG6" s="42"/>
-      <c r="AH6" s="43"/>
-      <c r="AI6" s="44"/>
-      <c r="AJ6" s="42"/>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="44"/>
-      <c r="AM6" s="42"/>
-      <c r="AN6" s="43"/>
-      <c r="AO6" s="44"/>
-      <c r="AP6" s="42"/>
-      <c r="AQ6" s="43"/>
-      <c r="AR6" s="44"/>
-    </row>
-    <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="38"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="40"/>
+      <c r="AA6" s="38"/>
+      <c r="AB6" s="39"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="39"/>
+      <c r="AF6" s="40"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="38"/>
+      <c r="AK6" s="39"/>
+      <c r="AL6" s="40"/>
+      <c r="AM6" s="38"/>
+      <c r="AN6" s="39"/>
+      <c r="AO6" s="40"/>
+      <c r="AP6" s="38"/>
+      <c r="AQ6" s="39"/>
+      <c r="AR6" s="40"/>
+    </row>
+    <row r="7" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="42"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="42"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="44"/>
-      <c r="AA7" s="42"/>
-      <c r="AB7" s="43"/>
-      <c r="AC7" s="44"/>
-      <c r="AD7" s="42"/>
-      <c r="AE7" s="43"/>
-      <c r="AF7" s="44"/>
-      <c r="AG7" s="42"/>
-      <c r="AH7" s="43"/>
-      <c r="AI7" s="44"/>
-      <c r="AJ7" s="42"/>
-      <c r="AK7" s="43"/>
-      <c r="AL7" s="44"/>
-      <c r="AM7" s="42"/>
-      <c r="AN7" s="43"/>
-      <c r="AO7" s="44"/>
-      <c r="AP7" s="42"/>
-      <c r="AQ7" s="43"/>
-      <c r="AR7" s="44"/>
-    </row>
-    <row r="8" spans="1:44" ht="92.25" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="39"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="38"/>
+      <c r="AE7" s="39"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="38"/>
+      <c r="AH7" s="39"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="38"/>
+      <c r="AK7" s="39"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="38"/>
+      <c r="AN7" s="39"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="38"/>
+      <c r="AQ7" s="39"/>
+      <c r="AR7" s="40"/>
+    </row>
+    <row r="8" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="44"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="44"/>
-      <c r="U8" s="42"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="44"/>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="43"/>
-      <c r="Z8" s="44"/>
-      <c r="AA8" s="42"/>
-      <c r="AB8" s="43"/>
-      <c r="AC8" s="44"/>
-      <c r="AD8" s="42"/>
-      <c r="AE8" s="43"/>
-      <c r="AF8" s="44"/>
-      <c r="AG8" s="42"/>
-      <c r="AH8" s="43"/>
-      <c r="AI8" s="44"/>
-      <c r="AJ8" s="42"/>
-      <c r="AK8" s="43"/>
-      <c r="AL8" s="44"/>
-      <c r="AM8" s="42"/>
-      <c r="AN8" s="43"/>
-      <c r="AO8" s="44"/>
-      <c r="AP8" s="42"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="44"/>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B9" s="13"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="42"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="42"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="44"/>
-      <c r="AA9" s="42"/>
-      <c r="AB9" s="43"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="42"/>
-      <c r="AE9" s="43"/>
-      <c r="AF9" s="44"/>
-      <c r="AG9" s="42"/>
-      <c r="AH9" s="43"/>
-      <c r="AI9" s="44"/>
-      <c r="AJ9" s="42"/>
-      <c r="AK9" s="43"/>
-      <c r="AL9" s="44"/>
-      <c r="AM9" s="42"/>
-      <c r="AN9" s="43"/>
-      <c r="AO9" s="44"/>
-      <c r="AP9" s="42"/>
-      <c r="AQ9" s="43"/>
-      <c r="AR9" s="44"/>
-    </row>
-    <row r="10" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="1"/>
-      <c r="B10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="38"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="39"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="39"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="39"/>
+      <c r="AF8" s="40"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="39"/>
+      <c r="AI8" s="40"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="39"/>
+      <c r="AL8" s="40"/>
+      <c r="AM8" s="38"/>
+      <c r="AN8" s="39"/>
+      <c r="AO8" s="40"/>
+      <c r="AP8" s="38"/>
+      <c r="AQ8" s="39"/>
+      <c r="AR8" s="40"/>
+    </row>
+    <row r="9" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="B9" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="39"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="38"/>
+      <c r="AB9" s="39"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="38"/>
+      <c r="AE9" s="39"/>
+      <c r="AF9" s="40"/>
+      <c r="AG9" s="38"/>
+      <c r="AH9" s="39"/>
+      <c r="AI9" s="40"/>
+      <c r="AJ9" s="38"/>
+      <c r="AK9" s="39"/>
+      <c r="AL9" s="40"/>
+      <c r="AM9" s="38"/>
+      <c r="AN9" s="39"/>
+      <c r="AO9" s="40"/>
+      <c r="AP9" s="38"/>
+      <c r="AQ9" s="39"/>
+      <c r="AR9" s="40"/>
+    </row>
+    <row r="10" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B10" s="41"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="44"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="42"/>
+      <c r="Y10" s="43"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="42"/>
+      <c r="AB10" s="43"/>
+      <c r="AC10" s="44"/>
+      <c r="AD10" s="42"/>
+      <c r="AE10" s="43"/>
+      <c r="AF10" s="44"/>
+      <c r="AG10" s="42"/>
+      <c r="AH10" s="43"/>
+      <c r="AI10" s="44"/>
+      <c r="AJ10" s="42"/>
+      <c r="AK10" s="43"/>
+      <c r="AL10" s="44"/>
+      <c r="AM10" s="42"/>
+      <c r="AN10" s="43"/>
+      <c r="AO10" s="44"/>
+      <c r="AP10" s="42"/>
+      <c r="AQ10" s="43"/>
+      <c r="AR10" s="44"/>
+    </row>
+    <row r="11" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1"/>
+      <c r="B11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="30">
-        <f>AVERAGE(C4:C9)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30">
-        <f>AVERAGE(F4:F9)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="30">
-        <f>AVERAGE(I4:I9)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="31"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="30">
-        <f>AVERAGE(L4:L9)</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="31"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="30">
-        <f>AVERAGE(O4:O9)</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="30">
-        <f>AVERAGE(R4:R9)</f>
-        <v>0</v>
-      </c>
-      <c r="S10" s="31"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="30">
-        <f>AVERAGE(U4:U9)</f>
-        <v>0</v>
-      </c>
-      <c r="V10" s="31"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="30">
-        <f>AVERAGE(X4:X9)</f>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="30">
-        <f>AVERAGE(AA4:AA9)</f>
-        <v>0</v>
-      </c>
-      <c r="AB10" s="31"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="30">
-        <f>AVERAGE(AD4:AD9)</f>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="32"/>
-      <c r="AG10" s="30">
-        <f>AVERAGE(AG4:AG9)</f>
-        <v>0</v>
-      </c>
-      <c r="AH10" s="31"/>
-      <c r="AI10" s="32"/>
-      <c r="AJ10" s="30">
-        <f>AVERAGE(AJ4:AJ9)</f>
-        <v>0</v>
-      </c>
-      <c r="AK10" s="31"/>
-      <c r="AL10" s="32"/>
-      <c r="AM10" s="30">
-        <f>AVERAGE(AM4:AM9)</f>
-        <v>0</v>
-      </c>
-      <c r="AN10" s="31"/>
-      <c r="AO10" s="32"/>
-      <c r="AP10" s="30">
-        <f>AVERAGE(AP4:AP9)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="31"/>
-      <c r="AR10" s="32"/>
-    </row>
-    <row r="11" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="3"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="8"/>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="8"/>
-      <c r="AH11" s="8"/>
-      <c r="AI11" s="8"/>
-      <c r="AJ11" s="8"/>
-      <c r="AK11" s="8"/>
-      <c r="AL11" s="8"/>
-      <c r="AM11" s="8"/>
-      <c r="AN11" s="8"/>
-      <c r="AO11" s="8"/>
-      <c r="AP11" s="8"/>
-      <c r="AQ11" s="8"/>
-      <c r="AR11" s="8"/>
+      <c r="C11" s="45">
+        <f>AVERAGE(C4:C10)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="45"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="45">
+        <f>AVERAGE(F4:F10)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="45"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="45">
+        <f>AVERAGE(I4:I10)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="45"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="45">
+        <f>AVERAGE(L4:L10)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="45"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="45">
+        <f>AVERAGE(O4:O10)</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="45">
+        <f>AVERAGE(R4:R10)</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="45"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="45">
+        <f>AVERAGE(U4:U10)</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="45"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="45">
+        <f>AVERAGE(X4:X10)</f>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="45"/>
+      <c r="Z11" s="46"/>
+      <c r="AA11" s="45">
+        <f>AVERAGE(AA4:AA10)</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="45"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="45">
+        <f>AVERAGE(AD4:AD10)</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="45"/>
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="45">
+        <f>AVERAGE(AG4:AG10)</f>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="45"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="45">
+        <f>AVERAGE(AJ4:AJ10)</f>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="45"/>
+      <c r="AL11" s="46"/>
+      <c r="AM11" s="45">
+        <f>AVERAGE(AM4:AM10)</f>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="45"/>
+      <c r="AO11" s="46"/>
+      <c r="AP11" s="45">
+        <f>AVERAGE(AP4:AP10)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="45"/>
+      <c r="AR11" s="46"/>
     </row>
     <row r="12" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="9"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -4620,26 +4689,71 @@
       <c r="AQ46" s="8"/>
       <c r="AR46" s="8"/>
     </row>
+    <row r="47" spans="2:44" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B47" s="9"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
+      <c r="Q47" s="8"/>
+      <c r="R47" s="8"/>
+      <c r="S47" s="8"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="8"/>
+      <c r="V47" s="8"/>
+      <c r="W47" s="8"/>
+      <c r="X47" s="8"/>
+      <c r="Y47" s="8"/>
+      <c r="Z47" s="8"/>
+      <c r="AA47" s="8"/>
+      <c r="AB47" s="8"/>
+      <c r="AC47" s="8"/>
+      <c r="AD47" s="8"/>
+      <c r="AE47" s="8"/>
+      <c r="AF47" s="8"/>
+      <c r="AG47" s="8"/>
+      <c r="AH47" s="8"/>
+      <c r="AI47" s="8"/>
+      <c r="AJ47" s="8"/>
+      <c r="AK47" s="8"/>
+      <c r="AL47" s="8"/>
+      <c r="AM47" s="8"/>
+      <c r="AN47" s="8"/>
+      <c r="AO47" s="8"/>
+      <c r="AP47" s="8"/>
+      <c r="AQ47" s="8"/>
+      <c r="AR47" s="8"/>
+    </row>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="AM10:AO10"/>
-    <mergeCell ref="X10:Z10"/>
-    <mergeCell ref="AA10:AC10"/>
-    <mergeCell ref="AD10:AF10"/>
-    <mergeCell ref="AG10:AI10"/>
-    <mergeCell ref="AJ10:AL10"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="AM11:AO11"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="AA11:AC11"/>
+    <mergeCell ref="AD11:AF11"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="R11:T11"/>
     <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AP10:AR10"/>
+    <mergeCell ref="AP11:AR11"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:H11"/>
     <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="AG2:AI2"/>

--- a/activity/M03A04/M03A04_Modelacion1D.xlsx
+++ b/activity/M03A04/M03A04_Modelacion1D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4293A2D8-8F51-47FA-BCD3-B077C1961144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0472E559-A1BF-4344-AD4B-F52277124DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -569,27 +569,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -598,9 +577,6 @@
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -637,14 +613,38 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -762,7 +762,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="65000"/>
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -2063,25 +2063,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="27" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.45">
       <c r="B4" s="17" t="s">
@@ -2104,14 +2104,14 @@
       <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="28">
         <v>5</v>
       </c>
       <c r="D5" s="20">
         <f>Detalle!C11*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="21">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2121,14 +2121,14 @@
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="28">
         <v>5</v>
       </c>
       <c r="D6" s="20">
         <f>Detalle!F11*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="36"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="21">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2138,14 +2138,14 @@
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="28">
         <v>5</v>
       </c>
       <c r="D7" s="20">
         <f>Detalle!I11*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="36"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2155,14 +2155,14 @@
       <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="28">
         <v>5</v>
       </c>
       <c r="D8" s="20">
         <f>Detalle!L11*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="36"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2172,14 +2172,14 @@
       <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="28">
         <v>5</v>
       </c>
       <c r="D9" s="20">
         <f>Detalle!O11*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="36"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2189,14 +2189,14 @@
       <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="28">
         <v>5</v>
       </c>
       <c r="D10" s="20">
         <f>Detalle!R11*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="36"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2206,14 +2206,14 @@
       <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="28">
         <v>5</v>
       </c>
       <c r="D11" s="20">
         <f>Detalle!U11*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="36"/>
+      <c r="E11" s="28"/>
       <c r="F11" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2223,14 +2223,14 @@
       <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="28">
         <v>5</v>
       </c>
       <c r="D12" s="20">
         <f>Detalle!X11*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="36"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2240,14 +2240,14 @@
       <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="28">
         <v>5</v>
       </c>
       <c r="D13" s="20">
         <f>Detalle!AA11*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="36"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2257,14 +2257,14 @@
       <c r="B14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="28">
         <v>5</v>
       </c>
       <c r="D14" s="20">
         <f>Detalle!AD11*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2274,14 +2274,14 @@
       <c r="B15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="28">
         <v>5</v>
       </c>
       <c r="D15" s="20">
         <f>Detalle!AG11*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="36"/>
+      <c r="E15" s="28"/>
       <c r="F15" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2291,14 +2291,14 @@
       <c r="B16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="28">
         <v>5</v>
       </c>
       <c r="D16" s="20">
         <f>Detalle!AJ11*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="36"/>
+      <c r="E16" s="28"/>
       <c r="F16" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2308,52 +2308,52 @@
       <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="28">
         <v>5</v>
       </c>
       <c r="D17" s="20">
         <f>Detalle!AM11*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="36"/>
+      <c r="E17" s="28"/>
       <c r="F17" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="29">
         <v>5</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="25">
         <f>Detalle!AP11*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="33">
+      <c r="E18" s="29"/>
+      <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="34" t="str">
+      <c r="B19" s="39" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M03A04 en GitHub.</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="22"/>
@@ -2452,96 +2452,96 @@
     </row>
     <row r="2" spans="1:44" s="11" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10"/>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="26" t="str">
+      <c r="C2" s="44" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="26" t="str">
+      <c r="D2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="44" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="26" t="str">
+      <c r="G2" s="45"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="44" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="27"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="26" t="str">
+      <c r="J2" s="45"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="44" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="26" t="str">
+      <c r="M2" s="45"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="44" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="26" t="str">
+      <c r="P2" s="45"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="44" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="27"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="26" t="str">
+      <c r="S2" s="45"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="44" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="27"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="26" t="str">
+      <c r="V2" s="45"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="44" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="26" t="str">
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="44" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="27"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="26" t="str">
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="44" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="26" t="str">
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="46"/>
+      <c r="AG2" s="44" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="27"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="26" t="str">
+      <c r="AH2" s="45"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="44" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="27"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="26" t="str">
+      <c r="AK2" s="45"/>
+      <c r="AL2" s="46"/>
+      <c r="AM2" s="44" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="27"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="26" t="str">
+      <c r="AN2" s="45"/>
+      <c r="AO2" s="46"/>
+      <c r="AP2" s="44" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="28"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="46"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="30"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="14" t="s">
         <v>1</v>
       </c>
@@ -2673,446 +2673,446 @@
       <c r="B4" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="38">
-        <v>0</v>
-      </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="38">
-        <v>0</v>
-      </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="38">
-        <v>0</v>
-      </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="38">
-        <v>0</v>
-      </c>
-      <c r="M4" s="39"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="38">
-        <v>0</v>
-      </c>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="38">
-        <v>0</v>
-      </c>
-      <c r="S4" s="39"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="38">
-        <v>0</v>
-      </c>
-      <c r="V4" s="39"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="38">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="40"/>
-      <c r="AA4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="39"/>
-      <c r="AC4" s="40"/>
-      <c r="AD4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="39"/>
-      <c r="AF4" s="40"/>
-      <c r="AG4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="39"/>
-      <c r="AI4" s="40"/>
-      <c r="AJ4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="39"/>
-      <c r="AL4" s="40"/>
-      <c r="AM4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="39"/>
-      <c r="AO4" s="40"/>
-      <c r="AP4" s="38">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="39"/>
-      <c r="AR4" s="40"/>
+      <c r="C4" s="30">
+        <v>0</v>
+      </c>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="30">
+        <v>0</v>
+      </c>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="30">
+        <v>0</v>
+      </c>
+      <c r="J4" s="31"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="30">
+        <v>0</v>
+      </c>
+      <c r="M4" s="31"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="30">
+        <v>0</v>
+      </c>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="30">
+        <v>0</v>
+      </c>
+      <c r="S4" s="31"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="30">
+        <v>0</v>
+      </c>
+      <c r="V4" s="31"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="31"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="31"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="31"/>
+      <c r="AO4" s="32"/>
+      <c r="AP4" s="30">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="31"/>
+      <c r="AR4" s="32"/>
     </row>
     <row r="5" spans="1:44" ht="184.5" x14ac:dyDescent="0.45">
       <c r="B5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="39"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="39"/>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="39"/>
-      <c r="AC5" s="40"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="39"/>
-      <c r="AF5" s="40"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="39"/>
-      <c r="AI5" s="40"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="39"/>
-      <c r="AL5" s="40"/>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="39"/>
-      <c r="AO5" s="40"/>
-      <c r="AP5" s="38"/>
-      <c r="AQ5" s="39"/>
-      <c r="AR5" s="40"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="30"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="32"/>
+      <c r="AJ5" s="30"/>
+      <c r="AK5" s="31"/>
+      <c r="AL5" s="32"/>
+      <c r="AM5" s="30"/>
+      <c r="AN5" s="31"/>
+      <c r="AO5" s="32"/>
+      <c r="AP5" s="30"/>
+      <c r="AQ5" s="31"/>
+      <c r="AR5" s="32"/>
     </row>
     <row r="6" spans="1:44" ht="80.650000000000006" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="40"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="39"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="40"/>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="39"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="38"/>
-      <c r="AE6" s="39"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="38"/>
-      <c r="AH6" s="39"/>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="38"/>
-      <c r="AK6" s="39"/>
-      <c r="AL6" s="40"/>
-      <c r="AM6" s="38"/>
-      <c r="AN6" s="39"/>
-      <c r="AO6" s="40"/>
-      <c r="AP6" s="38"/>
-      <c r="AQ6" s="39"/>
-      <c r="AR6" s="40"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="31"/>
+      <c r="AI6" s="32"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="31"/>
+      <c r="AL6" s="32"/>
+      <c r="AM6" s="30"/>
+      <c r="AN6" s="31"/>
+      <c r="AO6" s="32"/>
+      <c r="AP6" s="30"/>
+      <c r="AQ6" s="31"/>
+      <c r="AR6" s="32"/>
     </row>
     <row r="7" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="40"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="39"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="38"/>
-      <c r="AE7" s="39"/>
-      <c r="AF7" s="40"/>
-      <c r="AG7" s="38"/>
-      <c r="AH7" s="39"/>
-      <c r="AI7" s="40"/>
-      <c r="AJ7" s="38"/>
-      <c r="AK7" s="39"/>
-      <c r="AL7" s="40"/>
-      <c r="AM7" s="38"/>
-      <c r="AN7" s="39"/>
-      <c r="AO7" s="40"/>
-      <c r="AP7" s="38"/>
-      <c r="AQ7" s="39"/>
-      <c r="AR7" s="40"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="32"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="32"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="31"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="31"/>
+      <c r="AF7" s="32"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="32"/>
+      <c r="AJ7" s="30"/>
+      <c r="AK7" s="31"/>
+      <c r="AL7" s="32"/>
+      <c r="AM7" s="30"/>
+      <c r="AN7" s="31"/>
+      <c r="AO7" s="32"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="31"/>
+      <c r="AR7" s="32"/>
     </row>
     <row r="8" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="39"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="39"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="40"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="39"/>
-      <c r="AC8" s="40"/>
-      <c r="AD8" s="38"/>
-      <c r="AE8" s="39"/>
-      <c r="AF8" s="40"/>
-      <c r="AG8" s="38"/>
-      <c r="AH8" s="39"/>
-      <c r="AI8" s="40"/>
-      <c r="AJ8" s="38"/>
-      <c r="AK8" s="39"/>
-      <c r="AL8" s="40"/>
-      <c r="AM8" s="38"/>
-      <c r="AN8" s="39"/>
-      <c r="AO8" s="40"/>
-      <c r="AP8" s="38"/>
-      <c r="AQ8" s="39"/>
-      <c r="AR8" s="40"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="30"/>
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="32"/>
+      <c r="AJ8" s="30"/>
+      <c r="AK8" s="31"/>
+      <c r="AL8" s="32"/>
+      <c r="AM8" s="30"/>
+      <c r="AN8" s="31"/>
+      <c r="AO8" s="32"/>
+      <c r="AP8" s="30"/>
+      <c r="AQ8" s="31"/>
+      <c r="AR8" s="32"/>
     </row>
     <row r="9" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="39"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="39"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="39"/>
-      <c r="Z9" s="40"/>
-      <c r="AA9" s="38"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="38"/>
-      <c r="AE9" s="39"/>
-      <c r="AF9" s="40"/>
-      <c r="AG9" s="38"/>
-      <c r="AH9" s="39"/>
-      <c r="AI9" s="40"/>
-      <c r="AJ9" s="38"/>
-      <c r="AK9" s="39"/>
-      <c r="AL9" s="40"/>
-      <c r="AM9" s="38"/>
-      <c r="AN9" s="39"/>
-      <c r="AO9" s="40"/>
-      <c r="AP9" s="38"/>
-      <c r="AQ9" s="39"/>
-      <c r="AR9" s="40"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="32"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="31"/>
+      <c r="Z9" s="32"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="31"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="31"/>
+      <c r="AF9" s="32"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="31"/>
+      <c r="AI9" s="32"/>
+      <c r="AJ9" s="30"/>
+      <c r="AK9" s="31"/>
+      <c r="AL9" s="32"/>
+      <c r="AM9" s="30"/>
+      <c r="AN9" s="31"/>
+      <c r="AO9" s="32"/>
+      <c r="AP9" s="30"/>
+      <c r="AQ9" s="31"/>
+      <c r="AR9" s="32"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B10" s="41"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="42"/>
-      <c r="Y10" s="43"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="42"/>
-      <c r="AB10" s="43"/>
-      <c r="AC10" s="44"/>
-      <c r="AD10" s="42"/>
-      <c r="AE10" s="43"/>
-      <c r="AF10" s="44"/>
-      <c r="AG10" s="42"/>
-      <c r="AH10" s="43"/>
-      <c r="AI10" s="44"/>
-      <c r="AJ10" s="42"/>
-      <c r="AK10" s="43"/>
-      <c r="AL10" s="44"/>
-      <c r="AM10" s="42"/>
-      <c r="AN10" s="43"/>
-      <c r="AO10" s="44"/>
-      <c r="AP10" s="42"/>
-      <c r="AQ10" s="43"/>
-      <c r="AR10" s="44"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="34"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="34"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="34"/>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="34"/>
+      <c r="AE10" s="35"/>
+      <c r="AF10" s="36"/>
+      <c r="AG10" s="34"/>
+      <c r="AH10" s="35"/>
+      <c r="AI10" s="36"/>
+      <c r="AJ10" s="34"/>
+      <c r="AK10" s="35"/>
+      <c r="AL10" s="36"/>
+      <c r="AM10" s="34"/>
+      <c r="AN10" s="35"/>
+      <c r="AO10" s="36"/>
+      <c r="AP10" s="34"/>
+      <c r="AQ10" s="35"/>
+      <c r="AR10" s="36"/>
     </row>
     <row r="11" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="42">
         <f>AVERAGE(C4:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="45"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="45">
+      <c r="D11" s="42"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="42">
         <f>AVERAGE(F4:F10)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="45"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="45">
+      <c r="G11" s="42"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="42">
         <f>AVERAGE(I4:I10)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="45"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="45">
+      <c r="J11" s="42"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="42">
         <f>AVERAGE(L4:L10)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="45"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="45">
+      <c r="M11" s="42"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="42">
         <f>AVERAGE(O4:O10)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="45">
+      <c r="P11" s="42"/>
+      <c r="Q11" s="43"/>
+      <c r="R11" s="42">
         <f>AVERAGE(R4:R10)</f>
         <v>0</v>
       </c>
-      <c r="S11" s="45"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="45">
+      <c r="S11" s="42"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="42">
         <f>AVERAGE(U4:U10)</f>
         <v>0</v>
       </c>
-      <c r="V11" s="45"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="45">
+      <c r="V11" s="42"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="42">
         <f>AVERAGE(X4:X10)</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="45"/>
-      <c r="Z11" s="46"/>
-      <c r="AA11" s="45">
+      <c r="Y11" s="42"/>
+      <c r="Z11" s="43"/>
+      <c r="AA11" s="42">
         <f>AVERAGE(AA4:AA10)</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="45"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="45">
+      <c r="AB11" s="42"/>
+      <c r="AC11" s="43"/>
+      <c r="AD11" s="42">
         <f>AVERAGE(AD4:AD10)</f>
         <v>0</v>
       </c>
-      <c r="AE11" s="45"/>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="45">
+      <c r="AE11" s="42"/>
+      <c r="AF11" s="43"/>
+      <c r="AG11" s="42">
         <f>AVERAGE(AG4:AG10)</f>
         <v>0</v>
       </c>
-      <c r="AH11" s="45"/>
-      <c r="AI11" s="46"/>
-      <c r="AJ11" s="45">
+      <c r="AH11" s="42"/>
+      <c r="AI11" s="43"/>
+      <c r="AJ11" s="42">
         <f>AVERAGE(AJ4:AJ10)</f>
         <v>0</v>
       </c>
-      <c r="AK11" s="45"/>
-      <c r="AL11" s="46"/>
-      <c r="AM11" s="45">
+      <c r="AK11" s="42"/>
+      <c r="AL11" s="43"/>
+      <c r="AM11" s="42">
         <f>AVERAGE(AM4:AM10)</f>
         <v>0</v>
       </c>
-      <c r="AN11" s="45"/>
-      <c r="AO11" s="46"/>
-      <c r="AP11" s="45">
+      <c r="AN11" s="42"/>
+      <c r="AO11" s="43"/>
+      <c r="AP11" s="42">
         <f>AVERAGE(AP4:AP10)</f>
         <v>0</v>
       </c>
-      <c r="AQ11" s="45"/>
-      <c r="AR11" s="46"/>
+      <c r="AQ11" s="42"/>
+      <c r="AR11" s="43"/>
     </row>
     <row r="12" spans="1:44" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="3"/>
@@ -4736,19 +4736,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="AA11:AC11"/>
-    <mergeCell ref="AD11:AF11"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="R11:T11"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP11:AR11"/>
     <mergeCell ref="C2:E2"/>
@@ -4765,6 +4752,19 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L2:N2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="AM11:AO11"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="AA11:AC11"/>
+    <mergeCell ref="AD11:AF11"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="R11:T11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
